--- a/results/ftse_feasibility.xlsx
+++ b/results/ftse_feasibility.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -481,146 +481,114 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>Before costs (£37.70 in all) the scanner made £-13.96; trading every signal the opposite way would have made £-38.45 after costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>The scanner does not clearly beat chance: filters cannot create an edge that is not there, so the improvement has to come from the entry signal itself or from the exits.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>B0. + breakout still past the zone by 0 typical candle ranges: did not help (average per trade £-0.15 v £-0.14; 356 trades)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>B1. + breakout still past the zone by 0.1 typical candle ranges: helped in one half only (average per trade £-0.15 v £-0.14; 353 trades)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+          <t>B0. + breakout still past the zone by 0 typical candle ranges: did not help, still loses money (average per trade £-0.15 v £-0.14; 356 trades)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>B2. + breakout still past the zone by 0.25 typical candle ranges: did not help (average per trade £-0.17 v £-0.14; 343 trades)</t>
+          <t>B1. + breakout still past the zone by 0.1 typical candle ranges: helped in one half only, still loses money (average per trade £-0.15 v £-0.14; 353 trades)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>B3. + breakout still past the zone by 0.5 typical candle ranges: did not help (average per trade £-0.18 v £-0.14; 326 trades)</t>
+          <t>B2. + breakout still past the zone by 0.25 typical candle ranges: did not help, still loses money (average per trade £-0.17 v £-0.14; 343 trades)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C. + at least 75% of the planned stop room left: helped in one half only (average per trade £-0.16 v £-0.14; 316 trades)</t>
+          <t>B3. + breakout still past the zone by 0.5 typical candle ranges: did not help, still loses money (average per trade £-0.18 v £-0.14; 326 trades)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>D. + stop not already traded through that day: helped in both halves (average per trade £-0.06 v £-0.14; 84 trades)</t>
+          <t>C. + at least 75% of the planned stop room left: helped in one half only, still loses money (average per trade £-0.16 v £-0.14; 316 trades)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>E. + no trades in a sideways regime: helped in both halves (average per trade £-0.13 v £-0.14; 381 trades)</t>
+          <t>D. + stop not already traded through that day: helped in both halves, still loses money (average per trade £-0.06 v £-0.14; 84 trades)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>F. + zone at least 2 trading hours old: did not help (average per trade £-0.14 v £-0.14; 377 trades)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+          <t>E. + no trades in a sideways regime: helped in both halves, still loses money (average per trade £-0.13 v £-0.14; 381 trades)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Self-search found and confirmed: Only trades where zone age (trading minutes) is 4.25e+03 to 7.65e+03 (gain £+25.21 on the first half, £+17.24 on the unseen second half).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+          <t>F. + zone at least 2 trading hours old: did not help, still loses money (average per trade £-0.14 v £-0.14; 377 trades)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Self-search found and confirmed: Only trades where fill v 9 EMA in trade's direction (%) is under 0.14 (gain £+24.74 on the first half, £+22.27 on the unseen second half).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+          <t>Self-search: no candidate held up on the unseen second half.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Self-search found and confirmed: Skip trades where stop already traded through is Yes (gain £+24.01 on the first half, £+31.30 on the unseen second half).</t>
+          <t>Exits: best was 'Half the target' with £-27.25 v £-51.66 for the current exit (not better in both halves).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Self-search found and confirmed: Only trades where weekday is Thursday (gain £+22.32 on the first half, £+22.31 on the unseen second half).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Self-search found and confirmed: Only trades where signal volume v normal is under 0.3 (gain £+21.36 on the first half, £+27.06 on the unseen second half).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Self-search found and confirmed: Only trades where opening gap in trade's direction (%) is -0.23 to 0.27 (gain £+21.25 on the first half, £+23.13 on the unseen second half).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Exits: best was 'Half the target' with £-27.25 v £-51.66 for the current exit (not better in both halves).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
           <t>All results are paper research on about 60 days of one market period. Nothing changes live trading without Phil's agreement.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="15">
     <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A15:L15"/>
     <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A21:L21"/>
-    <mergeCell ref="A12:L12"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A11:L11"/>
     <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A13:L13"/>
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A6:L6"/>
     <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A12:L12"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A6:L6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1092,7 +1060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1108,6 +1076,8 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -1157,35 +1127,45 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Trades removed (both halves)</t>
+          <t>Average kept, first half (£)</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Gain, first half (£)</t>
+          <t>All trades, first half (£)</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Gain, second half (£)</t>
+          <t>Average kept, second half (£)</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Average kept, first half (£)</t>
+          <t>All trades, second half (£)</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Average kept, second half (£)</t>
+          <t>Improvement, first half (£ per trade)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
+          <t>Improvement, second half (£ per trade)</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
           <t>Candidate</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Random subsets as good (second half)</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Check on second half</t>
         </is>
@@ -1194,68 +1174,74 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Only trades where zone age (trading minutes) is 4.25e+03 to 7.65e+03</t>
+          <t>Skip trades where stop already traded through is Yes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>zone_age_minutes</t>
+          <t>stop_pretested</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>4.25e+03 to 7.65e+03</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>283</v>
+        <v>34</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.1173</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>25.21</v>
+        <v>-0.1101</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>17.24</v>
+        <v>-0.0047</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.08309999999999999</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>-0.4309</v>
-      </c>
-      <c r="L5" s="4" t="b">
+        <v>-0.1622</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.2273</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="M5" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed on unseen half</t>
+      <c r="N5" s="4" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>Not confirmed: random trades of the same number did as well too often</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Only trades where fill v 9 EMA in trade's direction (%) is under 0.14</t>
+          <t>Only trades where zone age (trading minutes) is 4.25e+03 to 7.65e+03</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>fill_vs_ema9_toward_trade_pct</t>
+          <t>zone_age_minutes</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>under 0.14</t>
+          <t>4.25e+03 to 7.65e+03</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1264,83 +1250,95 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>243</v>
+        <v>33</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.08309999999999999</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>24.74</v>
+        <v>-0.1101</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>22.27</v>
+        <v>-0.4309</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.0767</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>-0.1242</v>
-      </c>
-      <c r="L6" s="4" t="b">
+        <v>-0.1622</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.1932</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>-0.2687</v>
+      </c>
+      <c r="M6" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed on unseen half</t>
+      <c r="N6" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>Not confirmed: did not help on the second half</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where stop already traded through is Yes</t>
+          <t>Only trades where fill v 9 EMA in trade's direction (%) is under 0.14</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>stop_pretested</t>
+          <t>fill_vs_ema9_toward_trade_pct</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>under 0.14</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>310</v>
+        <v>74</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.0767</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>24.01</v>
+        <v>-0.1101</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>31.3</v>
+        <v>-0.1242</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.1173</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>-0.0047</v>
-      </c>
-      <c r="L7" s="4" t="b">
+        <v>-0.1622</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.1867</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="M7" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed on unseen half</t>
+      <c r="N7" s="4" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>Not confirmed: random trades of the same number did as well too often</t>
         </is>
       </c>
     </row>
@@ -1371,27 +1369,33 @@
       <c r="F8" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>297</v>
+      <c r="G8" s="6" t="n">
+        <v>0.0589</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>22.32</v>
+        <v>-0.1101</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>22.31</v>
+        <v>-0.2128</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.0589</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>-0.2128</v>
-      </c>
-      <c r="L8" s="4" t="b">
+        <v>-0.1622</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>-0.0506</v>
+      </c>
+      <c r="M8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed on unseen half</t>
+      <c r="N8" s="4" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>Not confirmed: did not help on the second half</t>
         </is>
       </c>
     </row>
@@ -1422,44 +1426,50 @@
       <c r="F9" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>299</v>
+      <c r="G9" s="6" t="n">
+        <v>0.0254</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>21.36</v>
+        <v>-0.1101</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>27.06</v>
+        <v>-0.1467</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.0254</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>-0.1467</v>
-      </c>
-      <c r="L9" s="4" t="b">
+        <v>-0.1622</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0.1355</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="M9" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed on unseen half</t>
+      <c r="N9" s="4" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Not confirmed: random trades of the same number did as well too often</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Only trades where opening gap in trade's direction (%) is -0.23 to 0.27</t>
+          <t>Only trades where zone touches is under 4</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>gap_toward_trade_pct</t>
+          <t>zone_touches</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>-0.23 to 0.27</t>
+          <t>under 4</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1468,32 +1478,38 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>256</v>
+        <v>56</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.0204</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>21.25</v>
+        <v>-0.1101</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>23.13</v>
+        <v>-0.1789</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>-0.1515</v>
-      </c>
-      <c r="L10" s="4" t="b">
+        <v>-0.1622</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>-0.0168</v>
+      </c>
+      <c r="M10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed on unseen half</t>
+      <c r="N10" s="4" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Not confirmed: did not help on the second half</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M117"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -1528,6 +1544,8 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -1570,35 +1588,45 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Trades removed (both halves)</t>
+          <t>Average kept, first half (£)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Gain, first half (£)</t>
+          <t>All trades, first half (£)</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Gain, second half (£)</t>
+          <t>Average kept, second half (£)</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Average kept, first half (£)</t>
+          <t>All trades, second half (£)</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Average kept, second half (£)</t>
+          <t>Improvement, first half (£ per trade)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
+          <t>Improvement, second half (£ per trade)</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
           <t>Candidate</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Random subsets as good (second half)</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Check on second half</t>
         </is>
@@ -1607,68 +1635,74 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Only trades where zone age (trading minutes) is 4.25e+03 to 7.65e+03</t>
+          <t>Skip trades where stop already traded through is Yes</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>zone_age_minutes</t>
+          <t>stop_pretested</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>4.25e+03 to 7.65e+03</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>283</v>
+        <v>34</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1173</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>25.21</v>
+        <v>-0.1101</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>17.24</v>
+        <v>-0.0047</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.08309999999999999</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>-0.4309</v>
-      </c>
-      <c r="L4" s="4" t="b">
+        <v>-0.1622</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0.2273</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="M4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed on unseen half</t>
+      <c r="N4" s="4" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>Not confirmed: random trades of the same number did as well too often</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Only trades where fill v 9 EMA in trade's direction (%) is under 0.14</t>
+          <t>Only trades where stop already traded through is No</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>fill_vs_ema9_toward_trade_pct</t>
+          <t>stop_pretested</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>under 0.14</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1677,100 +1711,106 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>243</v>
+        <v>34</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.1173</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>24.74</v>
+        <v>-0.1101</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>22.27</v>
+        <v>-0.0047</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.0767</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>-0.1242</v>
-      </c>
-      <c r="L5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed on unseen half</t>
-        </is>
-      </c>
+        <v>-0.1622</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.2273</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="M5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where stop already traded through is Yes</t>
+          <t>Only trades where zone age (trading minutes) is 4.25e+03 to 7.65e+03</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>stop_pretested</t>
+          <t>zone_age_minutes</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>4.25e+03 to 7.65e+03</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>310</v>
+      <c r="G6" s="6" t="n">
+        <v>0.08309999999999999</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>24.01</v>
+        <v>-0.1101</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>31.3</v>
+        <v>-0.4309</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.1173</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>-0.0047</v>
-      </c>
-      <c r="L6" s="4" t="b">
+        <v>-0.1622</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.1932</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>-0.2687</v>
+      </c>
+      <c r="M6" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed on unseen half</t>
+      <c r="N6" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>Not confirmed: did not help on the second half</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Only trades where stop already traded through is No</t>
+          <t>Only trades where fill v 9 EMA in trade's direction (%) is under 0.14</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>stop_pretested</t>
+          <t>fill_vs_ema9_toward_trade_pct</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>under 0.14</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1779,30 +1819,40 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>310</v>
+        <v>74</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.0767</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>24.01</v>
+        <v>-0.1101</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>31.3</v>
+        <v>-0.1242</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.1173</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>-0.0047</v>
-      </c>
-      <c r="L7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.1867</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="M7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>Not confirmed: random trades of the same number did as well too often</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1831,91 +1881,107 @@
       <c r="F8" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>297</v>
+      <c r="G8" s="6" t="n">
+        <v>0.0589</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>22.32</v>
+        <v>-0.1101</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>22.31</v>
+        <v>-0.2128</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.0589</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>-0.2128</v>
-      </c>
-      <c r="L8" s="4" t="b">
+        <v>-0.1622</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>-0.0506</v>
+      </c>
+      <c r="M8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed on unseen half</t>
+      <c r="N8" s="4" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>Not confirmed: did not help on the second half</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where zone age (trading minutes) is over 7.65e+03</t>
+          <t>Only trades where signal volume v normal is under 0.3</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>zone_age_minutes</t>
+          <t>signal_volume_ratio</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>over 7.65e+03</t>
+          <t>under 0.3</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>184</v>
+        <v>30</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.0254</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>22.22</v>
+        <v>-0.1101</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>12.93</v>
+        <v>-0.1467</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>-0.261</v>
-      </c>
-      <c r="L9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M9" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0.1355</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="M9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Not confirmed: random trades of the same number did as well too often</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Only trades where signal volume v normal is under 0.3</t>
+          <t>Only trades where zone touches is under 4</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>signal_volume_ratio</t>
+          <t>zone_touches</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>under 0.3</t>
+          <t>under 4</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1924,100 +1990,106 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>299</v>
+        <v>56</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.0204</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>21.36</v>
+        <v>-0.1101</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>27.06</v>
+        <v>-0.1789</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.0254</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>-0.1467</v>
-      </c>
-      <c r="L10" s="4" t="b">
+        <v>-0.1622</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>-0.0168</v>
+      </c>
+      <c r="M10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed on unseen half</t>
+      <c r="N10" s="4" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Not confirmed: did not help on the second half</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Only trades where opening gap in trade's direction (%) is -0.23 to 0.27</t>
+          <t>Skip trades where zone age (trading minutes) is over 7.65e+03</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>gap_toward_trade_pct</t>
+          <t>zone_age_minutes</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>-0.23 to 0.27</t>
+          <t>over 7.65e+03</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>256</v>
+        <v>71</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0.017</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>21.25</v>
+        <v>-0.1101</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>23.13</v>
+        <v>-0.261</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>-0.1515</v>
-      </c>
-      <c r="L11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed on unseen half</t>
-        </is>
-      </c>
+        <v>-0.1622</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>-0.0988</v>
+      </c>
+      <c r="M11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Only trades where zone touches is under 4</t>
+          <t>Only trades where opening gap in trade's direction (%) is -0.23 to 0.27</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>zone_touches</t>
+          <t>gap_toward_trade_pct</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>under 4</t>
+          <t>-0.23 to 0.27</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -2026,30 +2098,34 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>271</v>
+        <v>55</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.0168</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>21.16</v>
+        <v>-0.1101</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>21.44</v>
+        <v>-0.1515</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.0204</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>-0.1789</v>
-      </c>
-      <c r="L12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M12" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="M12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2078,25 +2154,29 @@
       <c r="F13" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>257</v>
+      <c r="G13" s="6" t="n">
+        <v>-0.0015</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>20.05</v>
+        <v>-0.1101</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>23.02</v>
+        <v>-0.1455</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>-0.0015</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>-0.1455</v>
-      </c>
-      <c r="L13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M13" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="M13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2125,181 +2205,197 @@
       <c r="F14" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="G14" s="4" t="n">
-        <v>276</v>
+      <c r="G14" s="6" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>19.16</v>
+        <v>-0.1101</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>29.21</v>
+        <v>-0.0523</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>-0.0169</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>-0.0523</v>
-      </c>
-      <c r="L14" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.09320000000000001</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="M14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Only trades where stop room band is 75-90%</t>
+          <t>Skip trades where stop room left at fill (%) is over 124</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>fill_room_band</t>
+          <t>fill_room_pct</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>75-90%</t>
+          <t>over 124</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>326</v>
+        <v>136</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.0229</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>18.89</v>
+        <v>-0.1101</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>29.17</v>
+        <v>-0.1361</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-0.0521</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>-0.0848</v>
-      </c>
-      <c r="L15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M15" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="M15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Only trades where weekday is Wednesday</t>
+          <t>Skip trades where zone touches is 4 to 5</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>zone_touches</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>4 to 5</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>300</v>
+        <v>123</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>18.64</v>
+        <v>-0.1101</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>21.1</v>
+        <v>-0.1562</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-0.0375</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="L16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M16" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0.0834</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where zone touches is 4 to 5</t>
+          <t>Only trades where weekday is Wednesday</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>zone_touches</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>4 to 5</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>123</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>163</v>
+        <v>37</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.0375</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>17.71</v>
+        <v>-0.1101</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>12.25</v>
+        <v>-0.28</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>-0.0267</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>-0.1562</v>
-      </c>
-      <c r="L17" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M17" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>-0.1178</v>
+      </c>
+      <c r="M17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Only trades where hour of entry is over 9</t>
+          <t>Only trades where stop room left at fill (%) is under 97.7</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>hour</t>
+          <t>fill_room_pct</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>over 9</t>
+          <t>under 97.7</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -2308,139 +2404,151 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>256</v>
+        <v>78</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-0.0448</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>17.43</v>
+        <v>-0.1101</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>17.9</v>
+        <v>-0.1291</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>-0.0521</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>-0.1965</v>
-      </c>
-      <c r="L18" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0.0653</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="M18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Only trades where stop room left at fill (%) is under 97.7</t>
+          <t>Skip trades where fill v 9 EMA in trade's direction (%) is over 0.42</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>fill_room_pct</t>
+          <t>fill_vs_ema9_toward_trade_pct</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>under 97.7</t>
+          <t>over 0.42</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>238</v>
+        <v>128</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.0476</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>17.41</v>
+        <v>-0.1101</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>21.39</v>
+        <v>-0.0688</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-0.0448</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>-0.1291</v>
-      </c>
-      <c r="L19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M19" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="M19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where stop room left at fill (%) is over 124</t>
+          <t>Only trades where zone age (trading minutes) is under 4.25e+03</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>fill_room_pct</t>
+          <t>zone_age_minutes</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>over 124</t>
+          <t>under 4.25e+03</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>136</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>118</v>
+        <v>38</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.049</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>17.32</v>
+        <v>-0.1101</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>12.95</v>
+        <v>-0.1134</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-0.0229</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>-0.1361</v>
-      </c>
-      <c r="L20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M20" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="M20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Only trades where zone age (trading minutes) is under 4.25e+03</t>
+          <t>Only trades where regime is Mixed</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>zone_age_minutes</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>under 4.25e+03</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2449,35 +2557,39 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>278</v>
+        <v>107</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-0.0491</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>17.15</v>
+        <v>-0.1101</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>27.15</v>
+        <v>-0.1889</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-0.049</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>-0.1134</v>
-      </c>
-      <c r="L21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M21" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>-0.0267</v>
+      </c>
+      <c r="M21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Only trades where stop room band is 50-75%</t>
+          <t>Only trades where stop room band is 75-90%</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2487,7 +2599,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>50-75%</t>
+          <t>75-90%</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -2496,45 +2608,49 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>309</v>
+        <v>27</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.0521</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>17.04</v>
+        <v>-0.1101</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>23.56</v>
+        <v>-0.0848</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>-0.1033</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>-0.2079</v>
-      </c>
-      <c r="L22" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="M22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Only trades where zone touches is over 5</t>
+          <t>Only trades where hour of entry is over 9</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>zone_touches</t>
+          <t>hour</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>over 5</t>
+          <t>over 9</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2543,45 +2659,49 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>269</v>
+        <v>69</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.0521</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>16.69</v>
+        <v>-0.1101</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>22.27</v>
+        <v>-0.1965</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-0.08409999999999999</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>-0.1372</v>
-      </c>
-      <c r="L23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>-0.0344</v>
+      </c>
+      <c r="M23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Only trades where weekday is Monday</t>
+          <t>Only trades where 9 EMA v 20 SMA is Down</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>ema_state</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -2590,129 +2710,141 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>304</v>
+        <v>58</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>-0.0522</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>16.46</v>
+        <v>-0.1101</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>23.9</v>
+        <v>-0.1428</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-0.115</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>-0.1844</v>
-      </c>
-      <c r="L24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M24" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="M24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Only trades where trends agreeing (0-3) is under 1</t>
+          <t>Skip trades where regime is Trending</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>trends_agreeing</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>under 1</t>
+          <t>Trending</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>306</v>
+        <v>114</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.0563</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>16.28</v>
+        <v>-0.1101</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>27.12</v>
+        <v>-0.2029</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-0.117</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>-0.1142</v>
-      </c>
-      <c r="L25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M25" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>-0.0407</v>
+      </c>
+      <c r="M25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where signal still intact at fill is Yes</t>
+          <t>Only trades where trends agreeing (0-3) is 1 to 2</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>signal_intact</t>
+          <t>trends_agreeing</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1 to 2</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>260</v>
+        <v>107</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.0635</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>16.28</v>
+        <v>-0.1101</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>24.95</v>
+        <v>-0.1686</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>-0.0643</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>-0.1142</v>
-      </c>
-      <c r="L26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M26" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="M26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Only trades where signal still intact at fill is No</t>
+          <t>Skip trades where signal still intact at fill is Yes</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -2722,12 +2854,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -2736,40 +2868,44 @@
       <c r="F27" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="G27" s="4" t="n">
-        <v>260</v>
+      <c r="G27" s="6" t="n">
+        <v>-0.0643</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>16.28</v>
+        <v>-0.1101</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>24.95</v>
+        <v>-0.1142</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>-0.0643</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>-0.1142</v>
-      </c>
-      <c r="L27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M27" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>0.0457</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="M27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Only trades where 9 EMA v 20 SMA is Down</t>
+          <t>Only trades where signal still intact at fill is No</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>ema_state</t>
+          <t>signal_intact</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2778,45 +2914,49 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>240</v>
+        <v>57</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>-0.0643</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>16.02</v>
+        <v>-0.1101</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>23.18</v>
+        <v>-0.1142</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-0.0522</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>-0.1428</v>
-      </c>
-      <c r="L28" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M28" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0.0457</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="M28" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where stop room band is 90%+</t>
+          <t>Skip trades where hour of entry is under 8.67</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>fill_room_band</t>
+          <t>hour</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>90%+</t>
+          <t>under 8.67</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2825,186 +2965,202 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>258</v>
+        <v>137</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-0.06469999999999999</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>15.79</v>
+        <v>-0.1101</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>21.27</v>
+        <v>-0.1709</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-0.0806</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>-0.1568</v>
-      </c>
-      <c r="L29" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M29" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="M29" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" s="4" t="n"/>
+      <c r="O29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Only trades where fill past the zone (%) is under -0.0867</t>
+          <t>Skip trades where opening gap in trade's direction (%) is over 0.27</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>fill_zone_margin_pct</t>
+          <t>gap_toward_trade_pct</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>under -0.0867</t>
+          <t>over 0.27</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>263</v>
+        <v>121</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>-0.0713</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>15.58</v>
+        <v>-0.1101</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>23.44</v>
+        <v>-0.1298</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-0.07480000000000001</v>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>-0.1513</v>
-      </c>
-      <c r="L30" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M30" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.0323</v>
+      </c>
+      <c r="M30" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Only trades where regime is Mixed</t>
+          <t>Skip trades where weekday is Friday</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>regime</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>173</v>
+        <v>164</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.0728</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>15.38</v>
+        <v>-0.1101</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>11.25</v>
+        <v>-0.1799</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-0.0491</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>-0.1889</v>
-      </c>
-      <c r="L31" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M31" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="M31" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Only trades where target / typical day is 0.52 to 0.73</t>
+          <t>Skip trades where 9 EMA v 20 SMA is Up</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>target_vs_daily_range</t>
+          <t>ema_state</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>0.52 to 0.73</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>255</v>
+        <v>98</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.0733</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>15.37</v>
+        <v>-0.1101</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>11.68</v>
+        <v>-0.2023</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-0.0745</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>-0.341</v>
-      </c>
-      <c r="L32" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M32" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>-0.0402</v>
+      </c>
+      <c r="M32" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Only trades where 9 EMA v 20 SMA is Flat</t>
+          <t>Only trades where hour of entry is 8.67 to 9</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ema_state</t>
+          <t>hour</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Flat</t>
+          <t>8.67 to 9</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3013,45 +3169,49 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>293</v>
+        <v>68</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.074</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>15.24</v>
+        <v>-0.1101</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>19.91</v>
+        <v>-0.1449</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-0.1114</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>-0.2888</v>
-      </c>
-      <c r="L33" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M33" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="M33" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Only trades where hour of entry is 8.67 to 9</t>
+          <t>Only trades where target / typical day is 0.52 to 0.73</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>hour</t>
+          <t>target_vs_daily_range</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>8.67 to 9</t>
+          <t>0.52 to 0.73</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -3060,45 +3220,49 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>239</v>
+        <v>58</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>-0.0745</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>14.96</v>
+        <v>-0.1101</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>21.61</v>
+        <v>-0.341</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>-0.074</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>-0.1449</v>
-      </c>
-      <c r="L34" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M34" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>-0.1789</v>
+      </c>
+      <c r="M34" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Only trades where quality score is under 55.5</t>
+          <t>Only trades where fill past the zone (%) is under -0.0867</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>fill_zone_margin_pct</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>under 55.5</t>
+          <t>under -0.0867</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -3110,42 +3274,46 @@
         <v>61</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>247</v>
+        <v>53</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>-0.07480000000000001</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>14.88</v>
+        <v>-0.1101</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>15.54</v>
+        <v>-0.1513</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>-0.0862</v>
-      </c>
-      <c r="K35" s="6" t="n">
-        <v>-0.2307</v>
-      </c>
-      <c r="L35" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M35" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="M35" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where regime is Trending</t>
+          <t>Skip trades where trends agreeing (0-3) is over 2</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>regime</t>
+          <t>trends_agreeing</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Trending</t>
+          <t>over 2</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -3154,45 +3322,49 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>161</v>
+        <v>145</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>-0.0759</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>14.4</v>
+        <v>-0.1101</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>8.33</v>
+        <v>-0.1543</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>-0.0563</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>-0.2029</v>
-      </c>
-      <c r="L36" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M36" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="M36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" s="4" t="n"/>
+      <c r="O36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where fill v 9 EMA in trade's direction (%) is over 0.42</t>
+          <t>Skip trades where stop room band is 90%+</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>fill_vs_ema9_toward_trade_pct</t>
+          <t>fill_room_band</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>over 0.42</t>
+          <t>90%+</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3201,139 +3373,151 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>126</v>
+        <v>65</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>-0.0806</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>14.29</v>
+        <v>-0.1101</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>22.65</v>
+        <v>-0.1568</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>-0.0476</v>
-      </c>
-      <c r="K37" s="6" t="n">
-        <v>-0.0688</v>
-      </c>
-      <c r="L37" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M37" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="M37" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Only trades where fill past the zone (%) is -0.0867 to 0.169</t>
+          <t>Skip trades where fill v 9 EMA in trade's direction (%) is 0.14 to 0.42</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>fill_zone_margin_pct</t>
+          <t>fill_vs_ema9_toward_trade_pct</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>-0.0867 to 0.169</t>
+          <t>0.14 to 0.42</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>251</v>
+        <v>140</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>-0.0808</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>13.84</v>
+        <v>-0.1101</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>26.2</v>
+        <v>-0.2274</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>-0.1033</v>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>-0.0809</v>
-      </c>
-      <c r="L38" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M38" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>-0.0653</v>
+      </c>
+      <c r="M38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38" s="4" t="n"/>
+      <c r="O38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Only trades where setup is Breakout</t>
+          <t>Skip trades where opening gap in trade's direction (%) is under -0.23</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>gap_toward_trade_pct</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>under -0.23</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>214</v>
+        <v>128</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>-0.0814</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>13.81</v>
+        <v>-0.1101</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>12.33</v>
+        <v>-0.1881</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>-0.0959</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>-0.1972</v>
-      </c>
-      <c r="L39" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M39" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="M39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where setup is Range</t>
+          <t>Skip trades where signal volume v normal is over 0.7</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>signal_volume_ratio</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>over 0.7</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -3342,92 +3526,100 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>214</v>
+        <v>118</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>-0.0819</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>13.81</v>
+        <v>-0.1101</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>12.33</v>
+        <v>-0.1509</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>-0.0959</v>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v>-0.1972</v>
-      </c>
-      <c r="L40" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M40" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>0.0282</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="M40" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Only trades where quality score is 55.5 to 65.5</t>
+          <t>Skip trades where signal volume v normal is 0.3 to 0.7</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>signal_volume_ratio</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>55.5 to 65.5</t>
+          <t>0.3 to 0.7</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>254</v>
+        <v>106</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>-0.0819</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>13.22</v>
+        <v>-0.1101</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>22.89</v>
+        <v>-0.1703</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>-0.1134</v>
-      </c>
-      <c r="K41" s="6" t="n">
-        <v>-0.1382</v>
-      </c>
-      <c r="L41" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M41" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="M41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" s="4" t="n"/>
+      <c r="O41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Only trades where target / typical day is under 0.52</t>
+          <t>Only trades where zone touches is over 5</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>target_vs_daily_range</t>
+          <t>zone_touches</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>under 0.52</t>
+          <t>over 5</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -3436,92 +3628,100 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>261</v>
+        <v>67</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>-0.08409999999999999</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>13.21</v>
+        <v>-0.1101</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>26.5</v>
+        <v>-0.1372</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>-0.1175</v>
-      </c>
-      <c r="K42" s="6" t="n">
-        <v>-0.08699999999999999</v>
-      </c>
-      <c r="L42" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M42" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="M42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Only trades where trends agreeing (0-3) is 1 to 2</t>
+          <t>Skip trades where weekday is Tuesday</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>trends_agreeing</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1 to 2</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>160</v>
+        <v>151</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>-0.0858</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>13.15</v>
+        <v>-0.1101</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>13.42</v>
+        <v>-0.1923</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-0.0635</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>-0.1686</v>
-      </c>
-      <c r="L43" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M43" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>-0.0301</v>
+      </c>
+      <c r="M43" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Only trades where weekday is Tuesday</t>
+          <t>Only trades where quality score is under 55.5</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>score</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>under 55.5</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3530,45 +3730,49 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>296</v>
+        <v>69</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>-0.0862</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>12.44</v>
+        <v>-0.1101</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>29.03</v>
+        <v>-0.2307</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>-0.2026</v>
-      </c>
-      <c r="K44" s="6" t="n">
-        <v>-0.0565</v>
-      </c>
-      <c r="L44" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M44" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>-0.06859999999999999</v>
+      </c>
+      <c r="M44" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N44" s="4" t="n"/>
+      <c r="O44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where hour of entry is under 8.67</t>
+          <t>Skip trades where planned stop (%) is over 0.63</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>hour</t>
+          <t>planned_stop_pct</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>under 8.67</t>
+          <t>over 0.63</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3577,139 +3781,151 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>137</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>118</v>
+        <v>112</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>-0.08649999999999999</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>12.25</v>
+        <v>-0.1101</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>8.050000000000001</v>
+        <v>-0.1269</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-0.06469999999999999</v>
-      </c>
-      <c r="K45" s="6" t="n">
-        <v>-0.1709</v>
-      </c>
-      <c r="L45" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M45" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="M45" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N45" s="4" t="n"/>
+      <c r="O45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Only trades where quality score is over 65.5</t>
+          <t>Skip trades where planned stop (%) is 0.36 to 0.63</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>planned_stop_pct</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>over 65.5</t>
+          <t>0.36 to 0.63</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>253</v>
+        <v>125</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>-0.08890000000000001</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>12.18</v>
+        <v>-0.1101</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>24.49</v>
+        <v>-0.156</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>-0.1305</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>-0.1106</v>
-      </c>
-      <c r="L46" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M46" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="M46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Only trades where target / typical day is over 0.73</t>
+          <t>Skip trades where fill past the zone (%) is over 0.169</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>target_vs_daily_range</t>
+          <t>fill_zone_margin_pct</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>over 0.73</t>
+          <t>over 0.169</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>238</v>
+        <v>118</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>-0.089</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>11.7</v>
+        <v>-0.1101</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>24.74</v>
+        <v>-0.1125</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-0.1407</v>
-      </c>
-      <c r="K47" s="6" t="n">
-        <v>-0.0851</v>
-      </c>
-      <c r="L47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M47" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="M47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where opening gap in trade's direction (%) is over 0.27</t>
+          <t>Skip trades where target / typical day is over 0.73</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>gap_toward_trade_pct</t>
+          <t>target_vs_daily_range</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>over 0.27</t>
+          <t>over 0.73</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3721,42 +3937,46 @@
         <v>123</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>121</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>133</v>
+        <v>115</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>-0.0951</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>11.37</v>
+        <v>-0.1101</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>15.75</v>
+        <v>-0.2151</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-0.0713</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>-0.1298</v>
-      </c>
-      <c r="L48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M48" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="M48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where signal volume v normal is 0.3 to 0.7</t>
+          <t>Skip trades where setup is Range</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>signal_volume_ratio</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>0.3 to 0.7</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3765,92 +3985,100 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>163</v>
+        <v>97</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>-0.0959</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>11.29</v>
+        <v>-0.1101</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>13.41</v>
+        <v>-0.1972</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-0.0819</v>
-      </c>
-      <c r="K49" s="6" t="n">
-        <v>-0.1703</v>
-      </c>
-      <c r="L49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M49" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="M49" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where 9 EMA v 20 SMA is Up</t>
+          <t>Only trades where setup is Breakout</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>ema_state</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>156</v>
+        <v>97</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>-0.0959</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>11.12</v>
+        <v>-0.1101</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>11.63</v>
+        <v>-0.1972</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-0.0733</v>
-      </c>
-      <c r="K50" s="6" t="n">
-        <v>-0.2023</v>
-      </c>
-      <c r="L50" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M50" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="M50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Only trades where fill past the zone (%) is over 0.169</t>
+          <t>Only trades where direction is Long</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>fill_zone_margin_pct</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>over 0.169</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3859,139 +4087,151 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>240</v>
+        <v>107</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>-0.0979</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>10.86</v>
+        <v>-0.1101</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>13.28</v>
+        <v>-0.1015</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-0.1521</v>
-      </c>
-      <c r="K51" s="6" t="n">
-        <v>-0.2392</v>
-      </c>
-      <c r="L51" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M51" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>0.0607</v>
+      </c>
+      <c r="M51" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Only trades where trends agreeing (0-3) is over 2</t>
+          <t>Skip trades where direction is Short</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>trends_agreeing</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>over 2</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>288</v>
+        <v>107</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>-0.0979</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>10.85</v>
+        <v>-0.1101</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>22.38</v>
+        <v>-0.1015</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-0.2322</v>
-      </c>
-      <c r="K52" s="6" t="n">
-        <v>-0.1853</v>
-      </c>
-      <c r="L52" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M52" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>0.0607</v>
+      </c>
+      <c r="M52" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Only trades where planned stop (%) is over 0.63</t>
+          <t>Skip trades where quality score is over 65.5</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>planned_stop_pct</t>
+          <t>score</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>over 0.63</t>
+          <t>over 65.5</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="G53" s="4" t="n">
-        <v>236</v>
+        <v>131</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>-0.0998</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>10.72</v>
+        <v>-0.1101</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>14.21</v>
+        <v>-0.1869</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-0.1597</v>
-      </c>
-      <c r="K53" s="6" t="n">
-        <v>-0.2104</v>
-      </c>
-      <c r="L53" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M53" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>-0.0248</v>
+      </c>
+      <c r="M53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Only trades where weekday is Friday</t>
+          <t>Only trades where fill past the zone (%) is -0.0867 to 0.169</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>fill_zone_margin_pct</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>-0.0867 to 0.169</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -4000,139 +4240,151 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>311</v>
+        <v>65</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>-0.1033</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>10.7</v>
+        <v>-0.1101</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>29.5</v>
+        <v>-0.0809</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-0.2622</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>-0.0653</v>
-      </c>
-      <c r="L54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M54" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="M54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N54" s="4" t="n"/>
+      <c r="O54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where direction is Long</t>
+          <t>Only trades where stop room band is 50-75%</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>fill_room_band</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>50-75%</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>215</v>
+        <v>38</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>-0.1033</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>10.57</v>
+        <v>-0.1101</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>10.86</v>
+        <v>-0.2079</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-0.1276</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>-0.2368</v>
-      </c>
-      <c r="L55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M55" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="M55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Only trades where direction is Short</t>
+          <t>Skip trades where target / typical day is under 0.52</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>target_vs_daily_range</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>under 0.52</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>215</v>
+        <v>137</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>-0.1065</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>10.57</v>
+        <v>-0.1101</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>10.86</v>
+        <v>-0.1934</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>-0.1276</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>-0.2368</v>
-      </c>
-      <c r="L56" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M56" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>-0.0313</v>
+      </c>
+      <c r="M56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N56" s="4" t="n"/>
+      <c r="O56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where fill v 9 EMA in trade's direction (%) is 0.14 to 0.42</t>
+          <t>Skip trades where quality score is 55.5 to 65.5</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>fill_vs_ema9_toward_trade_pct</t>
+          <t>score</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>0.14 to 0.42</t>
+          <t>55.5 to 65.5</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -4141,233 +4393,253 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="G57" s="4" t="n">
-        <v>117</v>
+        <v>132</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>-0.1084</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>10.45</v>
+        <v>-0.1101</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-0.38</v>
+        <v>-0.1734</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>-0.0808</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>-0.2274</v>
-      </c>
-      <c r="L57" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M57" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="M57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Only trades where planned stop (%) is 0.36 to 0.63</t>
+          <t>Skip trades where trends agreeing (0-3) is under 1</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>planned_stop_pct</t>
+          <t>trends_agreeing</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>0.36 to 0.63</t>
+          <t>under 1</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>66</v>
+        <v>150</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>242</v>
+        <v>156</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>-0.1085</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>10.4</v>
+        <v>-0.1101</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>19.5</v>
+        <v>-0.1738</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>-0.1476</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>-0.1733</v>
-      </c>
-      <c r="L58" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M58" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>-0.0117</v>
+      </c>
+      <c r="M58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" s="4" t="n"/>
+      <c r="O58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Only trades where opening gap in trade's direction (%) is under -0.23</t>
+          <t>Skip trades where weekday is Monday</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>gap_toward_trade_pct</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>under -0.23</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="G59" s="4" t="n">
-        <v>254</v>
+        <v>153</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>-0.109</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>10.26</v>
+        <v>-0.1101</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>24.08</v>
+        <v>-0.1562</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>-0.1733</v>
-      </c>
-      <c r="K59" s="6" t="n">
-        <v>-0.1118</v>
-      </c>
-      <c r="L59" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M59" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K59" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N59" s="4" t="n"/>
+      <c r="O59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Only trades where signal volume v normal is over 0.7</t>
+          <t>Skip trades where 9 EMA v 20 SMA is Flat</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>signal_volume_ratio</t>
+          <t>ema_state</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>over 0.7</t>
+          <t>Flat</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>241</v>
+        <v>154</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>-0.1096</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>10.07</v>
+        <v>-0.1101</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>17.81</v>
+        <v>-0.1293</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>-0.1678</v>
-      </c>
-      <c r="K60" s="6" t="n">
-        <v>-0.1796</v>
-      </c>
-      <c r="L60" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M60" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="M60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N60" s="4" t="n"/>
+      <c r="O60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where signal volume v normal is over 0.7</t>
+          <t>Only trades where 9 EMA v 20 SMA is Flat</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>signal_volume_ratio</t>
+          <t>ema_state</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>over 0.7</t>
+          <t>Flat</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="G61" s="4" t="n">
-        <v>136</v>
+        <v>40</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>-0.1114</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>10.07</v>
+        <v>-0.1101</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>13.65</v>
+        <v>-0.2888</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>-0.0819</v>
-      </c>
-      <c r="K61" s="6" t="n">
-        <v>-0.1509</v>
-      </c>
-      <c r="L61" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M61" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K61" s="4" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>-0.1266</v>
+      </c>
+      <c r="M61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N61" s="4" t="n"/>
+      <c r="O61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where opening gap in trade's direction (%) is under -0.23</t>
+          <t>Skip trades where stop room band is 50-75%</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>gap_toward_trade_pct</t>
+          <t>fill_room_band</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>under -0.23</t>
+          <t>50-75%</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -4376,186 +4648,202 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>123</v>
+        <v>156</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>-0.1114</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>9.880000000000001</v>
+        <v>-0.1101</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>7.38</v>
+        <v>-0.151</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>-0.0814</v>
-      </c>
-      <c r="K62" s="6" t="n">
-        <v>-0.1881</v>
-      </c>
-      <c r="L62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M62" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="M62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N62" s="4" t="n"/>
+      <c r="O62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where planned stop (%) is 0.36 to 0.63</t>
+          <t>Only trades where quality score is 55.5 to 65.5</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>planned_stop_pct</t>
+          <t>score</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>0.36 to 0.63</t>
+          <t>55.5 to 65.5</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>135</v>
+        <v>62</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>-0.1134</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>9.74</v>
+        <v>-0.1101</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>11.96</v>
+        <v>-0.1382</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>-0.08890000000000001</v>
-      </c>
-      <c r="K63" s="6" t="n">
-        <v>-0.156</v>
-      </c>
-      <c r="L63" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M63" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K63" s="4" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="M63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N63" s="4" t="n"/>
+      <c r="O63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Only trades where fill v 9 EMA in trade's direction (%) is 0.14 to 0.42</t>
+          <t>Skip trades where fill past the zone (%) is -0.0867 to 0.169</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>fill_vs_ema9_toward_trade_pct</t>
+          <t>fill_zone_margin_pct</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>0.14 to 0.42</t>
+          <t>-0.0867 to 0.169</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="G64" s="4" t="n">
-        <v>260</v>
+        <v>129</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>-0.1134</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>9.69</v>
+        <v>-0.1101</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>31.84</v>
+        <v>-0.2031</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>-0.1659</v>
-      </c>
-      <c r="K64" s="6" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="L64" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M64" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K64" s="4" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="M64" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N64" s="4" t="n"/>
+      <c r="O64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where direction is Short</t>
+          <t>Only trades where weekday is Monday</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>162</v>
+        <v>41</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>-0.115</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>9.57</v>
+        <v>-0.1101</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>20.6</v>
+        <v>-0.1844</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>-0.0979</v>
-      </c>
-      <c r="K65" s="6" t="n">
-        <v>-0.1015</v>
-      </c>
-      <c r="L65" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M65" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K65" s="4" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="M65" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N65" s="4" t="n"/>
+      <c r="O65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Only trades where direction is Long</t>
+          <t>Only trades where trends agreeing (0-3) is under 1</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>trends_agreeing</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>under 1</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -4564,92 +4852,100 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="G66" s="4" t="n">
-        <v>162</v>
+        <v>38</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>-0.117</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>9.57</v>
+        <v>-0.1101</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>20.6</v>
+        <v>-0.1142</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>-0.0979</v>
-      </c>
-      <c r="K66" s="6" t="n">
-        <v>-0.1015</v>
-      </c>
-      <c r="L66" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M66" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K66" s="4" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="M66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N66" s="4" t="n"/>
+      <c r="O66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where weekday is Friday</t>
+          <t>Only trades where target / typical day is under 0.52</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>target_vs_daily_range</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>under 0.52</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>147</v>
+        <v>59</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>164</v>
-      </c>
-      <c r="G67" s="4" t="n">
-        <v>66</v>
+        <v>57</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>-0.1175</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>9.44</v>
+        <v>-0.1101</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>1.96</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>-0.0728</v>
-      </c>
-      <c r="K67" s="6" t="n">
-        <v>-0.1799</v>
-      </c>
-      <c r="L67" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M67" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K67" s="4" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>0.0751</v>
+      </c>
+      <c r="M67" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where planned stop (%) is over 0.63</t>
+          <t>Skip trades where zone touches is over 5</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>planned_stop_pct</t>
+          <t>zone_touches</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>over 0.63</t>
+          <t>over 5</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -4658,45 +4954,49 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>141</v>
+        <v>127</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>-0.1175</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>9.42</v>
+        <v>-0.1101</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>17.25</v>
+        <v>-0.1754</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>-0.08649999999999999</v>
-      </c>
-      <c r="K68" s="6" t="n">
-        <v>-0.1269</v>
-      </c>
-      <c r="L68" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M68" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="M68" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N68" s="4" t="n"/>
+      <c r="O68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where trends agreeing (0-3) is over 2</t>
+          <t>Skip trades where setup is Breakout</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>trends_agreeing</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>over 2</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -4705,186 +5005,202 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="G69" s="4" t="n">
-        <v>89</v>
+        <v>97</v>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>-0.118</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>9.289999999999999</v>
+        <v>-0.1101</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>9.08</v>
+        <v>-0.1271</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>-0.0759</v>
-      </c>
-      <c r="K69" s="6" t="n">
-        <v>-0.1543</v>
-      </c>
-      <c r="L69" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M69" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K69" s="4" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="M69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where fill past the zone (%) is over 0.169</t>
+          <t>Only trades where setup is Range</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>fill_zone_margin_pct</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>over 0.169</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>137</v>
+        <v>97</v>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>-0.118</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>9.279999999999999</v>
+        <v>-0.1101</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>18.18</v>
+        <v>-0.1271</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>-0.089</v>
-      </c>
-      <c r="K70" s="6" t="n">
-        <v>-0.1125</v>
-      </c>
-      <c r="L70" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M70" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="M70" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N70" s="4" t="n"/>
+      <c r="O70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Only trades where 9 EMA v 20 SMA is Up</t>
+          <t>Skip trades where stop room band is 75-90%</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>ema_state</t>
+          <t>fill_room_band</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>75-90%</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="G71" s="4" t="n">
-        <v>221</v>
+        <v>167</v>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>-0.1188</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>9.02</v>
+        <v>-0.1101</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>19.83</v>
+        <v>-0.1747</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>-0.1853</v>
-      </c>
-      <c r="K71" s="6" t="n">
-        <v>-0.1211</v>
-      </c>
-      <c r="L71" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M71" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="L71" s="4" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="M71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71" s="4" t="n"/>
+      <c r="O71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Only trades where signal volume v normal is 0.3 to 0.7</t>
+          <t>Skip trades where quality score is under 55.5</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>signal_volume_ratio</t>
+          <t>score</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>0.3 to 0.7</t>
+          <t>under 55.5</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="G72" s="4" t="n">
-        <v>214</v>
+        <v>125</v>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>-0.122</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>8.85</v>
+        <v>-0.1101</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>18.05</v>
+        <v>-0.1243</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>-0.1505</v>
-      </c>
-      <c r="K72" s="6" t="n">
-        <v>-0.1524</v>
-      </c>
-      <c r="L72" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M72" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="M72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N72" s="4" t="n"/>
+      <c r="O72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Only trades where opening gap in trade's direction (%) is over 0.27</t>
+          <t>Only trades where stop room band is 90%+</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>gap_toward_trade_pct</t>
+          <t>fill_room_band</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>over 0.27</t>
+          <t>90%+</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -4893,45 +5209,49 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="G73" s="4" t="n">
-        <v>244</v>
+        <v>129</v>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>-0.1224</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>8.77</v>
+        <v>-0.1101</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>15.71</v>
+        <v>-0.1649</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>-0.1895</v>
-      </c>
-      <c r="K73" s="6" t="n">
-        <v>-0.2158</v>
-      </c>
-      <c r="L73" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M73" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="M73" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N73" s="4" t="n"/>
+      <c r="O73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where target / typical day is over 0.73</t>
+          <t>Skip trades where direction is Long</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>target_vs_daily_range</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>over 0.73</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -4940,139 +5260,151 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="G74" s="4" t="n">
-        <v>139</v>
+        <v>87</v>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>-0.1276</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>8.44</v>
+        <v>-0.1101</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>6.72</v>
+        <v>-0.2368</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>-0.0951</v>
-      </c>
-      <c r="K74" s="6" t="n">
-        <v>-0.2151</v>
-      </c>
-      <c r="L74" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M74" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>-0.0746</v>
+      </c>
+      <c r="M74" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N74" s="4" t="n"/>
+      <c r="O74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where quality score is over 65.5</t>
+          <t>Only trades where direction is Short</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>over 65.5</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>131</v>
-      </c>
-      <c r="G75" s="4" t="n">
-        <v>124</v>
+        <v>87</v>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>-0.1276</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>7.96</v>
+        <v>-0.1101</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>6.97</v>
+        <v>-0.2368</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>-0.0998</v>
-      </c>
-      <c r="K75" s="6" t="n">
-        <v>-0.1869</v>
-      </c>
-      <c r="L75" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M75" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K75" s="4" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="L75" s="4" t="n">
+        <v>-0.0746</v>
+      </c>
+      <c r="M75" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N75" s="4" t="n"/>
+      <c r="O75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Only trades where hour of entry is under 8.67</t>
+          <t>Skip trades where fill past the zone (%) is under -0.0867</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>hour</t>
+          <t>fill_zone_margin_pct</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>under 8.67</t>
+          <t>under -0.0867</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>259</v>
+        <v>141</v>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>-0.1277</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>7.89</v>
+        <v>-0.1101</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>23.41</v>
+        <v>-0.1662</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>-0.2008</v>
-      </c>
-      <c r="K76" s="6" t="n">
-        <v>-0.1412</v>
-      </c>
-      <c r="L76" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M76" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="M76" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N76" s="4" t="n"/>
+      <c r="O76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where weekday is Tuesday</t>
+          <t>Skip trades where target / typical day is 0.52 to 0.73</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>target_vs_daily_range</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>0.52 to 0.73</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -5081,45 +5413,49 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>151</v>
-      </c>
-      <c r="G77" s="4" t="n">
-        <v>81</v>
+        <v>136</v>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>-0.1292</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>7.7</v>
+        <v>-0.1101</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>2.43</v>
+        <v>-0.0859</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>-0.0858</v>
-      </c>
-      <c r="K77" s="6" t="n">
-        <v>-0.1923</v>
-      </c>
-      <c r="L77" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M77" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K77" s="4" t="n">
+        <v>-0.0191</v>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="M77" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N77" s="4" t="n"/>
+      <c r="O77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where trends agreeing (0-3) is 1 to 2</t>
+          <t>Skip trades where weekday is Wednesday</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>trends_agreeing</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>1 to 2</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -5128,92 +5464,100 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>217</v>
+        <v>157</v>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>-0.1303</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>6.99</v>
+        <v>-0.1101</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>18.04</v>
+        <v>-0.1344</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>-0.1801</v>
-      </c>
-      <c r="K78" s="6" t="n">
-        <v>-0.1543</v>
-      </c>
-      <c r="L78" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M78" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>-0.0203</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="M78" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N78" s="4" t="n"/>
+      <c r="O78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where target / typical day is under 0.52</t>
+          <t>Only trades where quality score is over 65.5</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>target_vs_daily_range</t>
+          <t>score</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>under 0.52</t>
+          <t>over 65.5</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>137</v>
-      </c>
-      <c r="G79" s="4" t="n">
-        <v>116</v>
+        <v>63</v>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>-0.1305</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>6.93</v>
+        <v>-0.1101</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>4.96</v>
+        <v>-0.1106</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>-0.1065</v>
-      </c>
-      <c r="K79" s="6" t="n">
-        <v>-0.1934</v>
-      </c>
-      <c r="L79" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M79" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K79" s="4" t="n">
+        <v>-0.0204</v>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="M79" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N79" s="4" t="n"/>
+      <c r="O79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where quality score is 55.5 to 65.5</t>
+          <t>Skip trades where signal still intact at fill is No</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>signal_intact</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>55.5 to 65.5</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -5222,45 +5566,49 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="G80" s="4" t="n">
-        <v>123</v>
+        <v>137</v>
+      </c>
+      <c r="G80" s="6" t="n">
+        <v>-0.1324</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>6.92</v>
+        <v>-0.1101</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>8.57</v>
+        <v>-0.1821</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>-0.1084</v>
-      </c>
-      <c r="K80" s="6" t="n">
-        <v>-0.1734</v>
-      </c>
-      <c r="L80" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M80" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K80" s="4" t="n">
+        <v>-0.0223</v>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M80" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N80" s="4" t="n"/>
+      <c r="O80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Only trades where setup is Range</t>
+          <t>Only trades where signal still intact at fill is Yes</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>signal_intact</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -5269,45 +5617,49 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="G81" s="4" t="n">
-        <v>163</v>
+        <v>137</v>
+      </c>
+      <c r="G81" s="6" t="n">
+        <v>-0.1324</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>6.33</v>
+        <v>-0.1101</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>19.13</v>
+        <v>-0.1821</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>-0.118</v>
-      </c>
-      <c r="K81" s="6" t="n">
-        <v>-0.1271</v>
-      </c>
-      <c r="L81" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M81" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K81" s="4" t="n">
+        <v>-0.0223</v>
+      </c>
+      <c r="L81" s="4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M81" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N81" s="4" t="n"/>
+      <c r="O81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where setup is Breakout</t>
+          <t>Skip trades where hour of entry is 8.67 to 9</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>hour</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>8.67 to 9</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -5316,45 +5668,49 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="G82" s="4" t="n">
-        <v>163</v>
+        <v>126</v>
+      </c>
+      <c r="G82" s="6" t="n">
+        <v>-0.1324</v>
       </c>
       <c r="H82" s="6" t="n">
-        <v>6.33</v>
+        <v>-0.1101</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>19.13</v>
+        <v>-0.1715</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>-0.118</v>
-      </c>
-      <c r="K82" s="6" t="n">
-        <v>-0.1271</v>
-      </c>
-      <c r="L82" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M82" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>-0.0223</v>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>-0.009299999999999999</v>
+      </c>
+      <c r="M82" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N82" s="4" t="n"/>
+      <c r="O82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where fill past the zone (%) is -0.0867 to 0.169</t>
+          <t>Skip trades where hour of entry is over 9</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>fill_zone_margin_pct</t>
+          <t>hour</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>-0.0867 to 0.169</t>
+          <t>over 9</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -5363,92 +5719,100 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="G83" s="4" t="n">
-        <v>126</v>
+        <v>125</v>
+      </c>
+      <c r="G83" s="6" t="n">
+        <v>-0.1331</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>6.3</v>
+        <v>-0.1101</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>5.26</v>
+        <v>-0.1432</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>-0.1134</v>
-      </c>
-      <c r="K83" s="6" t="n">
-        <v>-0.2031</v>
-      </c>
-      <c r="L83" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M83" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K83" s="4" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="M83" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N83" s="4" t="n"/>
+      <c r="O83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Only trades where fill v 9 EMA in trade's direction (%) is over 0.42</t>
+          <t>Skip trades where zone age (trading minutes) is under 4.25e+03</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>fill_vs_ema9_toward_trade_pct</t>
+          <t>zone_age_minutes</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>over 0.42</t>
+          <t>under 4.25e+03</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="G84" s="4" t="n">
-        <v>251</v>
+        <v>156</v>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v>-0.1406</v>
       </c>
       <c r="H84" s="6" t="n">
-        <v>5.85</v>
+        <v>-0.1101</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>8.81</v>
+        <v>-0.174</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>-0.2382</v>
-      </c>
-      <c r="K84" s="6" t="n">
-        <v>-0.3432</v>
-      </c>
-      <c r="L84" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M84" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K84" s="4" t="n">
+        <v>-0.0305</v>
+      </c>
+      <c r="L84" s="4" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="M84" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N84" s="4" t="n"/>
+      <c r="O84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Only trades where regime is Trending</t>
+          <t>Only trades where target / typical day is over 0.73</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>regime</t>
+          <t>target_vs_daily_range</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Trending</t>
+          <t>over 0.73</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -5457,45 +5821,49 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="G85" s="4" t="n">
-        <v>216</v>
+        <v>79</v>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>-0.1407</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>5.74</v>
+        <v>-0.1101</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>23.13</v>
+        <v>-0.0851</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>-0.1778</v>
-      </c>
-      <c r="K85" s="6" t="n">
-        <v>-0.1041</v>
-      </c>
-      <c r="L85" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M85" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K85" s="4" t="n">
+        <v>-0.0306</v>
+      </c>
+      <c r="L85" s="4" t="n">
+        <v>0.0771</v>
+      </c>
+      <c r="M85" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N85" s="4" t="n"/>
+      <c r="O85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where quality score is under 55.5</t>
+          <t>Skip trades where stop room left at fill (%) is under 97.7</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>fill_room_pct</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>under 55.5</t>
+          <t>under 97.7</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -5507,183 +5875,199 @@
         <v>122</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="G86" s="4" t="n">
-        <v>130</v>
+        <v>116</v>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>-0.1427</v>
       </c>
       <c r="H86" s="6" t="n">
-        <v>5.26</v>
+        <v>-0.1101</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>15.92</v>
+        <v>-0.1844</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>-0.122</v>
-      </c>
-      <c r="K86" s="6" t="n">
-        <v>-0.1243</v>
-      </c>
-      <c r="L86" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M86" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K86" s="4" t="n">
+        <v>-0.0327</v>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="M86" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N86" s="4" t="n"/>
+      <c r="O86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where hour of entry is 8.67 to 9</t>
+          <t>Only trades where planned stop (%) is 0.36 to 0.63</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>hour</t>
+          <t>planned_stop_pct</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>8.67 to 9</t>
+          <t>0.36 to 0.63</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>126</v>
-      </c>
-      <c r="G87" s="4" t="n">
-        <v>138</v>
+        <v>69</v>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>-0.1476</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>5.18</v>
+        <v>-0.1101</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>9.85</v>
+        <v>-0.1733</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>-0.1324</v>
-      </c>
-      <c r="K87" s="6" t="n">
-        <v>-0.1715</v>
-      </c>
-      <c r="L87" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M87" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K87" s="4" t="n">
+        <v>-0.0375</v>
+      </c>
+      <c r="L87" s="4" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="M87" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N87" s="4" t="n"/>
+      <c r="O87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where 9 EMA v 20 SMA is Flat</t>
+          <t>Only trades where signal volume v normal is 0.3 to 0.7</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>ema_state</t>
+          <t>signal_volume_ratio</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Flat</t>
+          <t>0.3 to 0.7</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>154</v>
-      </c>
-      <c r="G88" s="4" t="n">
-        <v>84</v>
+        <v>88</v>
+      </c>
+      <c r="G88" s="6" t="n">
+        <v>-0.1505</v>
       </c>
       <c r="H88" s="6" t="n">
-        <v>4.9</v>
+        <v>-0.1101</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>11.55</v>
+        <v>-0.1524</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>-0.1096</v>
-      </c>
-      <c r="K88" s="6" t="n">
-        <v>-0.1293</v>
-      </c>
-      <c r="L88" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M88" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K88" s="4" t="n">
+        <v>-0.0405</v>
+      </c>
+      <c r="L88" s="4" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="M88" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N88" s="4" t="n"/>
+      <c r="O88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where target / typical day is 0.52 to 0.73</t>
+          <t>Only trades where fill past the zone (%) is over 0.169</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>target_vs_daily_range</t>
+          <t>fill_zone_margin_pct</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>0.52 to 0.73</t>
+          <t>over 0.169</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>136</v>
-      </c>
-      <c r="G89" s="4" t="n">
-        <v>122</v>
+        <v>76</v>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>-0.1521</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>4.77</v>
+        <v>-0.1101</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>19.78</v>
+        <v>-0.2392</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>-0.1292</v>
-      </c>
-      <c r="K89" s="6" t="n">
-        <v>-0.0859</v>
-      </c>
-      <c r="L89" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M89" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K89" s="4" t="n">
+        <v>-0.0421</v>
+      </c>
+      <c r="L89" s="4" t="n">
+        <v>-0.077</v>
+      </c>
+      <c r="M89" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N89" s="4" t="n"/>
+      <c r="O89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where regime is Mixed</t>
+          <t>Skip trades where weekday is Thursday</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>regime</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -5692,45 +6076,49 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="G90" s="4" t="n">
-        <v>204</v>
+        <v>151</v>
+      </c>
+      <c r="G90" s="6" t="n">
+        <v>-0.1529</v>
       </c>
       <c r="H90" s="6" t="n">
-        <v>4.76</v>
+        <v>-0.1101</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>20.21</v>
+        <v>-0.1477</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>-0.1788</v>
-      </c>
-      <c r="K90" s="6" t="n">
-        <v>-0.1293</v>
-      </c>
-      <c r="L90" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M90" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K90" s="4" t="n">
+        <v>-0.0428</v>
+      </c>
+      <c r="L90" s="4" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="M90" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N90" s="4" t="n"/>
+      <c r="O90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where fill past the zone (%) is under -0.0867</t>
+          <t>Skip trades where planned stop (%) is under 0.36</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>fill_zone_margin_pct</t>
+          <t>planned_stop_pct</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>under -0.0867</t>
+          <t>under 0.36</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -5739,92 +6127,100 @@
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>141</v>
-      </c>
-      <c r="G91" s="4" t="n">
-        <v>114</v>
+        <v>151</v>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v>-0.1533</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>4.56</v>
+        <v>-0.1101</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>8.02</v>
+        <v>-0.1934</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>-0.1277</v>
-      </c>
-      <c r="K91" s="6" t="n">
-        <v>-0.1662</v>
-      </c>
-      <c r="L91" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M91" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K91" s="4" t="n">
+        <v>-0.0432</v>
+      </c>
+      <c r="L91" s="4" t="n">
+        <v>-0.0313</v>
+      </c>
+      <c r="M91" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N91" s="4" t="n"/>
+      <c r="O91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Only trades where stop room band is 90%+</t>
+          <t>Skip trades where 9 EMA v 20 SMA is Down</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>fill_room_band</t>
+          <t>ema_state</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>90%+</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="G92" s="4" t="n">
-        <v>119</v>
+        <v>136</v>
+      </c>
+      <c r="G92" s="6" t="n">
+        <v>-0.154</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>4.35</v>
+        <v>-0.1101</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>10.19</v>
+        <v>-0.1704</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>-0.1224</v>
-      </c>
-      <c r="K92" s="6" t="n">
-        <v>-0.1649</v>
-      </c>
-      <c r="L92" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M92" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K92" s="4" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="L92" s="4" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="M92" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N92" s="4" t="n"/>
+      <c r="O92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where 9 EMA v 20 SMA is Down</t>
+          <t>Skip trades where signal volume v normal is under 0.3</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>ema_state</t>
+          <t>signal_volume_ratio</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>under 0.3</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -5833,45 +6229,49 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>136</v>
-      </c>
-      <c r="G93" s="4" t="n">
-        <v>137</v>
+        <v>164</v>
+      </c>
+      <c r="G93" s="6" t="n">
+        <v>-0.1582</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>4.12</v>
+        <v>-0.1101</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>8.279999999999999</v>
+        <v>-0.165</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>-0.154</v>
-      </c>
-      <c r="K93" s="6" t="n">
-        <v>-0.1704</v>
-      </c>
-      <c r="L93" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M93" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K93" s="4" t="n">
+        <v>-0.0482</v>
+      </c>
+      <c r="L93" s="4" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="M93" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N93" s="4" t="n"/>
+      <c r="O93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where signal still intact at fill is No</t>
+          <t>Skip trades where zone touches is under 4</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>signal_intact</t>
+          <t>zone_touches</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>under 4</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -5880,45 +6280,49 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>137</v>
-      </c>
-      <c r="G94" s="4" t="n">
-        <v>117</v>
+        <v>138</v>
+      </c>
+      <c r="G94" s="6" t="n">
+        <v>-0.1591</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>3.86</v>
+        <v>-0.1101</v>
       </c>
       <c r="I94" s="6" t="n">
-        <v>6.51</v>
+        <v>-0.1554</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>-0.1324</v>
-      </c>
-      <c r="K94" s="6" t="n">
-        <v>-0.1821</v>
-      </c>
-      <c r="L94" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M94" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K94" s="4" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="L94" s="4" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="M94" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N94" s="4" t="n"/>
+      <c r="O94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Only trades where signal still intact at fill is Yes</t>
+          <t>Only trades where planned stop (%) is over 0.63</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>signal_intact</t>
+          <t>planned_stop_pct</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>over 0.63</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -5927,92 +6331,100 @@
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>137</v>
-      </c>
-      <c r="G95" s="4" t="n">
-        <v>117</v>
+        <v>82</v>
+      </c>
+      <c r="G95" s="6" t="n">
+        <v>-0.1597</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>3.86</v>
+        <v>-0.1101</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>6.51</v>
+        <v>-0.2104</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>-0.1324</v>
-      </c>
-      <c r="K95" s="6" t="n">
-        <v>-0.1821</v>
-      </c>
-      <c r="L95" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M95" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K95" s="4" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="L95" s="4" t="n">
+        <v>-0.0482</v>
+      </c>
+      <c r="M95" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N95" s="4" t="n"/>
+      <c r="O95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where trends agreeing (0-3) is under 1</t>
+          <t>Only trades where stop already traded through is Yes</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>trends_agreeing</t>
+          <t>stop_pretested</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>under 1</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
         <v>150</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>71</v>
+        <v>160</v>
+      </c>
+      <c r="G96" s="6" t="n">
+        <v>-0.1601</v>
       </c>
       <c r="H96" s="6" t="n">
-        <v>3.86</v>
+        <v>-0.1101</v>
       </c>
       <c r="I96" s="6" t="n">
-        <v>4.34</v>
+        <v>-0.1956</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>-0.1085</v>
-      </c>
-      <c r="K96" s="6" t="n">
-        <v>-0.1738</v>
-      </c>
-      <c r="L96" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M96" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K96" s="4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L96" s="4" t="n">
+        <v>-0.0335</v>
+      </c>
+      <c r="M96" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N96" s="4" t="n"/>
+      <c r="O96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where weekday is Monday</t>
+          <t>Skip trades where stop already traded through is No</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>stop_pretested</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -6021,45 +6433,49 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>153</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>73</v>
+        <v>160</v>
+      </c>
+      <c r="G97" s="6" t="n">
+        <v>-0.1601</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>3.68</v>
+        <v>-0.1101</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>7.56</v>
+        <v>-0.1956</v>
       </c>
       <c r="J97" s="6" t="n">
-        <v>-0.109</v>
-      </c>
-      <c r="K97" s="6" t="n">
-        <v>-0.1562</v>
-      </c>
-      <c r="L97" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M97" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K97" s="4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L97" s="4" t="n">
+        <v>-0.0335</v>
+      </c>
+      <c r="M97" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N97" s="4" t="n"/>
+      <c r="O97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where zone touches is over 5</t>
+          <t>Skip trades where stop room left at fill (%) is 97.7 to 124</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>zone_touches</t>
+          <t>fill_room_pct</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>over 5</t>
+          <t>97.7 to 124</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -6068,139 +6484,151 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>127</v>
-      </c>
-      <c r="G98" s="4" t="n">
-        <v>108</v>
+        <v>136</v>
+      </c>
+      <c r="G98" s="6" t="n">
+        <v>-0.1657</v>
       </c>
       <c r="H98" s="6" t="n">
-        <v>3.45</v>
+        <v>-0.1101</v>
       </c>
       <c r="I98" s="6" t="n">
-        <v>9.19</v>
+        <v>-0.1693</v>
       </c>
       <c r="J98" s="6" t="n">
-        <v>-0.1175</v>
-      </c>
-      <c r="K98" s="6" t="n">
-        <v>-0.1754</v>
-      </c>
-      <c r="L98" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M98" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K98" s="4" t="n">
+        <v>-0.0556</v>
+      </c>
+      <c r="L98" s="4" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="M98" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N98" s="4" t="n"/>
+      <c r="O98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where stop room band is 50-75%</t>
+          <t>Only trades where fill v 9 EMA in trade's direction (%) is 0.14 to 0.42</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>fill_room_band</t>
+          <t>fill_vs_ema9_toward_trade_pct</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>50-75%</t>
+          <t>0.14 to 0.42</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>153</v>
+        <v>63</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="G99" s="4" t="n">
-        <v>68</v>
+        <v>54</v>
+      </c>
+      <c r="G99" s="6" t="n">
+        <v>-0.1659</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>3.1</v>
+        <v>-0.1101</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>7.9</v>
+        <v>0.007</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>-0.1114</v>
-      </c>
-      <c r="K99" s="6" t="n">
-        <v>-0.151</v>
-      </c>
-      <c r="L99" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M99" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K99" s="4" t="n">
+        <v>-0.0558</v>
+      </c>
+      <c r="L99" s="4" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="M99" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N99" s="4" t="n"/>
+      <c r="O99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where zone age (trading minutes) is under 4.25e+03</t>
+          <t>Only trades where signal volume v normal is over 0.7</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>zone_age_minutes</t>
+          <t>signal_volume_ratio</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>under 4.25e+03</t>
+          <t>over 0.7</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="G100" s="4" t="n">
-        <v>99</v>
+        <v>76</v>
+      </c>
+      <c r="G100" s="6" t="n">
+        <v>-0.1678</v>
       </c>
       <c r="H100" s="6" t="n">
-        <v>2.99</v>
+        <v>-0.1101</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>4.31</v>
+        <v>-0.1796</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>-0.1406</v>
-      </c>
-      <c r="K100" s="6" t="n">
-        <v>-0.174</v>
-      </c>
-      <c r="L100" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M100" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K100" s="4" t="n">
+        <v>-0.0578</v>
+      </c>
+      <c r="L100" s="4" t="n">
+        <v>-0.0174</v>
+      </c>
+      <c r="M100" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N100" s="4" t="n"/>
+      <c r="O100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Only trades where stop room left at fill (%) is over 124</t>
+          <t>Only trades where opening gap in trade's direction (%) is under -0.23</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>fill_room_pct</t>
+          <t>gap_toward_trade_pct</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>over 124</t>
+          <t>under -0.23</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -6209,92 +6637,100 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="G101" s="4" t="n">
-        <v>259</v>
+        <v>66</v>
+      </c>
+      <c r="G101" s="6" t="n">
+        <v>-0.1733</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>2.82</v>
+        <v>-0.1101</v>
       </c>
       <c r="I101" s="6" t="n">
-        <v>18.51</v>
+        <v>-0.1118</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>-0.2887</v>
-      </c>
-      <c r="K101" s="6" t="n">
-        <v>-0.2233</v>
-      </c>
-      <c r="L101" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M101" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K101" s="4" t="n">
+        <v>-0.0633</v>
+      </c>
+      <c r="L101" s="4" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="M101" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N101" s="4" t="n"/>
+      <c r="O101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where stop room left at fill (%) is under 97.7</t>
+          <t>Only trades where regime is Trending</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>fill_room_pct</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>under 97.7</t>
+          <t>Trending</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="G102" s="4" t="n">
-        <v>139</v>
+        <v>80</v>
+      </c>
+      <c r="G102" s="6" t="n">
+        <v>-0.1778</v>
       </c>
       <c r="H102" s="6" t="n">
-        <v>2.73</v>
+        <v>-0.1101</v>
       </c>
       <c r="I102" s="6" t="n">
-        <v>10.07</v>
+        <v>-0.1041</v>
       </c>
       <c r="J102" s="6" t="n">
-        <v>-0.1427</v>
-      </c>
-      <c r="K102" s="6" t="n">
-        <v>-0.1844</v>
-      </c>
-      <c r="L102" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M102" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K102" s="4" t="n">
+        <v>-0.0677</v>
+      </c>
+      <c r="L102" s="4" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="M102" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N102" s="4" t="n"/>
+      <c r="O102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where hour of entry is over 9</t>
+          <t>Skip trades where regime is Mixed</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>hour</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>over 9</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -6303,92 +6739,100 @@
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="G103" s="4" t="n">
-        <v>121</v>
+        <v>87</v>
+      </c>
+      <c r="G103" s="6" t="n">
+        <v>-0.1788</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>2.71</v>
+        <v>-0.1101</v>
       </c>
       <c r="I103" s="6" t="n">
-        <v>13.56</v>
+        <v>-0.1293</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>-0.1331</v>
-      </c>
-      <c r="K103" s="6" t="n">
-        <v>-0.1432</v>
-      </c>
-      <c r="L103" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M103" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K103" s="4" t="n">
+        <v>-0.0688</v>
+      </c>
+      <c r="L103" s="4" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="M103" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N103" s="4" t="n"/>
+      <c r="O103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Only trades where zone touches is 4 to 5</t>
+          <t>Skip trades where trends agreeing (0-3) is 1 to 2</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>zone_touches</t>
+          <t>trends_agreeing</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>4 to 5</t>
+          <t>1 to 2</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="G104" s="4" t="n">
-        <v>214</v>
+        <v>87</v>
+      </c>
+      <c r="G104" s="6" t="n">
+        <v>-0.1801</v>
       </c>
       <c r="H104" s="6" t="n">
-        <v>2.43</v>
+        <v>-0.1101</v>
       </c>
       <c r="I104" s="6" t="n">
-        <v>19.21</v>
+        <v>-0.1543</v>
       </c>
       <c r="J104" s="6" t="n">
-        <v>-0.1925</v>
-      </c>
-      <c r="K104" s="6" t="n">
-        <v>-0.1725</v>
-      </c>
-      <c r="L104" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M104" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K104" s="4" t="n">
+        <v>-0.0701</v>
+      </c>
+      <c r="L104" s="4" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="M104" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N104" s="4" t="n"/>
+      <c r="O104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where weekday is Wednesday</t>
+          <t>Skip trades where opening gap in trade's direction (%) is -0.23 to 0.27</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>gap_toward_trade_pct</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>-0.23 to 0.27</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -6397,233 +6841,253 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>157</v>
-      </c>
-      <c r="G105" s="4" t="n">
-        <v>77</v>
+        <v>139</v>
+      </c>
+      <c r="G105" s="6" t="n">
+        <v>-0.1816</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>1.5</v>
+        <v>-0.1101</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>10.36</v>
+        <v>-0.1664</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>-0.1303</v>
-      </c>
-      <c r="K105" s="6" t="n">
-        <v>-0.1344</v>
-      </c>
-      <c r="L105" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M105" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K105" s="4" t="n">
+        <v>-0.0716</v>
+      </c>
+      <c r="L105" s="4" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="M105" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N105" s="4" t="n"/>
+      <c r="O105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where stop room band is 75-90%</t>
+          <t>Only trades where 9 EMA v 20 SMA is Up</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>fill_room_band</t>
+          <t>ema_state</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>75-90%</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>159</v>
+        <v>60</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="G106" s="4" t="n">
-        <v>51</v>
+        <v>96</v>
+      </c>
+      <c r="G106" s="6" t="n">
+        <v>-0.1853</v>
       </c>
       <c r="H106" s="6" t="n">
-        <v>1.25</v>
+        <v>-0.1101</v>
       </c>
       <c r="I106" s="6" t="n">
-        <v>2.29</v>
+        <v>-0.1211</v>
       </c>
       <c r="J106" s="6" t="n">
-        <v>-0.1188</v>
-      </c>
-      <c r="K106" s="6" t="n">
-        <v>-0.1747</v>
-      </c>
-      <c r="L106" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M106" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K106" s="4" t="n">
+        <v>-0.07530000000000001</v>
+      </c>
+      <c r="L106" s="4" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="M106" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N106" s="4" t="n"/>
+      <c r="O106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where planned stop (%) is under 0.36</t>
+          <t>Only trades where opening gap in trade's direction (%) is over 0.27</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>planned_stop_pct</t>
+          <t>gap_toward_trade_pct</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>under 0.36</t>
+          <t>over 0.27</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>151</v>
-      </c>
-      <c r="G107" s="4" t="n">
-        <v>101</v>
+        <v>73</v>
+      </c>
+      <c r="G107" s="6" t="n">
+        <v>-0.1895</v>
       </c>
       <c r="H107" s="6" t="n">
-        <v>0.98</v>
+        <v>-0.1101</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>2.25</v>
+        <v>-0.2158</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>-0.1533</v>
-      </c>
-      <c r="K107" s="6" t="n">
-        <v>-0.1934</v>
-      </c>
-      <c r="L107" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M107" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K107" s="4" t="n">
+        <v>-0.0794</v>
+      </c>
+      <c r="L107" s="4" t="n">
+        <v>-0.0536</v>
+      </c>
+      <c r="M107" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N107" s="4" t="n"/>
+      <c r="O107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where stop room left at fill (%) is 97.7 to 124</t>
+          <t>Only trades where zone touches is 4 to 5</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>fill_room_pct</t>
+          <t>zone_touches</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>97.7 to 124</t>
+          <t>4 to 5</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>136</v>
-      </c>
-      <c r="G108" s="4" t="n">
-        <v>120</v>
+        <v>71</v>
+      </c>
+      <c r="G108" s="6" t="n">
+        <v>-0.1925</v>
       </c>
       <c r="H108" s="6" t="n">
-        <v>0.09</v>
+        <v>-0.1101</v>
       </c>
       <c r="I108" s="6" t="n">
-        <v>8.44</v>
+        <v>-0.1725</v>
       </c>
       <c r="J108" s="6" t="n">
-        <v>-0.1657</v>
-      </c>
-      <c r="K108" s="6" t="n">
-        <v>-0.1693</v>
-      </c>
-      <c r="L108" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M108" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K108" s="4" t="n">
+        <v>-0.0824</v>
+      </c>
+      <c r="L108" s="4" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="M108" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N108" s="4" t="n"/>
+      <c r="O108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where zone touches is under 4</t>
+          <t>Only trades where hour of entry is under 8.67</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>zone_touches</t>
+          <t>hour</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>under 4</t>
+          <t>under 8.67</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>138</v>
-      </c>
-      <c r="G109" s="4" t="n">
-        <v>106</v>
+        <v>57</v>
+      </c>
+      <c r="G109" s="6" t="n">
+        <v>-0.2008</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>-1.02</v>
+        <v>-0.1101</v>
       </c>
       <c r="I109" s="6" t="n">
-        <v>10.02</v>
+        <v>-0.1412</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>-0.1591</v>
-      </c>
-      <c r="K109" s="6" t="n">
-        <v>-0.1554</v>
-      </c>
-      <c r="L109" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M109" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K109" s="4" t="n">
+        <v>-0.09080000000000001</v>
+      </c>
+      <c r="L109" s="4" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="M109" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N109" s="4" t="n"/>
+      <c r="O109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where opening gap in trade's direction (%) is -0.23 to 0.27</t>
+          <t>Skip trades where fill v 9 EMA in trade's direction (%) is under 0.14</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>gap_toward_trade_pct</t>
+          <t>fill_vs_ema9_toward_trade_pct</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>-0.23 to 0.27</t>
+          <t>under 0.14</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -6632,82 +7096,90 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>139</v>
-      </c>
-      <c r="G110" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
+      </c>
+      <c r="G110" s="6" t="n">
+        <v>-0.2011</v>
       </c>
       <c r="H110" s="6" t="n">
-        <v>-1.11</v>
+        <v>-0.1101</v>
       </c>
       <c r="I110" s="6" t="n">
-        <v>8.33</v>
+        <v>-0.1856</v>
       </c>
       <c r="J110" s="6" t="n">
-        <v>-0.1816</v>
-      </c>
-      <c r="K110" s="6" t="n">
-        <v>-0.1664</v>
-      </c>
-      <c r="L110" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M110" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K110" s="4" t="n">
+        <v>-0.0911</v>
+      </c>
+      <c r="L110" s="4" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="M110" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N110" s="4" t="n"/>
+      <c r="O110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where signal volume v normal is under 0.3</t>
+          <t>Only trades where weekday is Tuesday</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>signal_volume_ratio</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>under 0.3</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>164</v>
-      </c>
-      <c r="G111" s="4" t="n">
-        <v>78</v>
+        <v>43</v>
+      </c>
+      <c r="G111" s="6" t="n">
+        <v>-0.2026</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>-1.22</v>
+        <v>-0.1101</v>
       </c>
       <c r="I111" s="6" t="n">
-        <v>4.4</v>
+        <v>-0.0565</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>-0.1582</v>
-      </c>
-      <c r="K111" s="6" t="n">
-        <v>-0.165</v>
-      </c>
-      <c r="L111" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M111" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K111" s="4" t="n">
+        <v>-0.0926</v>
+      </c>
+      <c r="L111" s="4" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="M111" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N111" s="4" t="n"/>
+      <c r="O111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Only trades where zone age (trading minutes) is over 7.65e+03</t>
+          <t>Skip trades where zone age (trading minutes) is 4.25e+03 to 7.65e+03</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
@@ -6717,148 +7189,160 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>over 7.65e+03</t>
+          <t>4.25e+03 to 7.65e+03</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Only</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>123</v>
-      </c>
-      <c r="G112" s="4" t="n">
-        <v>193</v>
+        <v>161</v>
+      </c>
+      <c r="G112" s="6" t="n">
+        <v>-0.2066</v>
       </c>
       <c r="H112" s="6" t="n">
-        <v>-2.08</v>
+        <v>-0.1101</v>
       </c>
       <c r="I112" s="6" t="n">
-        <v>18.53</v>
+        <v>-0.1071</v>
       </c>
       <c r="J112" s="6" t="n">
-        <v>-0.3643</v>
-      </c>
-      <c r="K112" s="6" t="n">
-        <v>-0.1051</v>
-      </c>
-      <c r="L112" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M112" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K112" s="4" t="n">
+        <v>-0.09660000000000001</v>
+      </c>
+      <c r="L112" s="4" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="M112" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N112" s="4" t="n"/>
+      <c r="O112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where weekday is Thursday</t>
+          <t>Only trades where trends agreeing (0-3) is over 2</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>trends_agreeing</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>over 2</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>151</v>
-      </c>
-      <c r="G113" s="4" t="n">
-        <v>80</v>
+        <v>49</v>
+      </c>
+      <c r="G113" s="6" t="n">
+        <v>-0.2322</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>-2.18</v>
+        <v>-0.1101</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>9.15</v>
+        <v>-0.1853</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>-0.1529</v>
-      </c>
-      <c r="K113" s="6" t="n">
-        <v>-0.1477</v>
-      </c>
-      <c r="L113" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M113" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K113" s="4" t="n">
+        <v>-0.1222</v>
+      </c>
+      <c r="L113" s="4" t="n">
+        <v>-0.0231</v>
+      </c>
+      <c r="M113" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N113" s="4" t="n"/>
+      <c r="O113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where stop already traded through is No</t>
+          <t>Only trades where fill v 9 EMA in trade's direction (%) is over 0.42</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>stop_pretested</t>
+          <t>fill_vs_ema9_toward_trade_pct</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>over 0.42</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="G114" s="4" t="n">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="G114" s="6" t="n">
+        <v>-0.2382</v>
       </c>
       <c r="H114" s="6" t="n">
-        <v>-3.87</v>
+        <v>-0.1101</v>
       </c>
       <c r="I114" s="6" t="n">
-        <v>0.16</v>
+        <v>-0.3432</v>
       </c>
       <c r="J114" s="6" t="n">
-        <v>-0.1601</v>
-      </c>
-      <c r="K114" s="6" t="n">
-        <v>-0.1956</v>
-      </c>
-      <c r="L114" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M114" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K114" s="4" t="n">
+        <v>-0.1281</v>
+      </c>
+      <c r="L114" s="4" t="n">
+        <v>-0.181</v>
+      </c>
+      <c r="M114" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N114" s="4" t="n"/>
+      <c r="O114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>Only trades where stop already traded through is Yes</t>
+          <t>Only trades where weekday is Friday</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>stop_pretested</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -6867,82 +7351,90 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="G115" s="4" t="n">
-        <v>67</v>
+        <v>30</v>
+      </c>
+      <c r="G115" s="6" t="n">
+        <v>-0.2622</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>-3.87</v>
+        <v>-0.1101</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>0.16</v>
+        <v>-0.0653</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>-0.1601</v>
-      </c>
-      <c r="K115" s="6" t="n">
-        <v>-0.1956</v>
-      </c>
-      <c r="L115" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M115" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K115" s="4" t="n">
+        <v>-0.1522</v>
+      </c>
+      <c r="L115" s="4" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="M115" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N115" s="4" t="n"/>
+      <c r="O115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where fill v 9 EMA in trade's direction (%) is under 0.14</t>
+          <t>Only trades where stop room left at fill (%) is over 124</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>fill_vs_ema9_toward_trade_pct</t>
+          <t>fill_room_pct</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>under 0.14</t>
+          <t>over 124</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="G116" s="4" t="n">
-        <v>134</v>
+        <v>58</v>
+      </c>
+      <c r="G116" s="6" t="n">
+        <v>-0.2887</v>
       </c>
       <c r="H116" s="6" t="n">
-        <v>-4.6</v>
+        <v>-0.1101</v>
       </c>
       <c r="I116" s="6" t="n">
-        <v>9.19</v>
+        <v>-0.2233</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>-0.2011</v>
-      </c>
-      <c r="K116" s="6" t="n">
-        <v>-0.1856</v>
-      </c>
-      <c r="L116" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M116" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K116" s="4" t="n">
+        <v>-0.1786</v>
+      </c>
+      <c r="L116" s="4" t="n">
+        <v>-0.0611</v>
+      </c>
+      <c r="M116" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N116" s="4" t="n"/>
+      <c r="O116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>Skip trades where zone age (trading minutes) is 4.25e+03 to 7.65e+03</t>
+          <t>Only trades where zone age (trading minutes) is over 7.65e+03</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -6952,39 +7444,43 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>4.25e+03 to 7.65e+03</t>
+          <t>over 7.65e+03</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Only</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>161</v>
-      </c>
-      <c r="G117" s="4" t="n">
-        <v>94</v>
+        <v>123</v>
+      </c>
+      <c r="G117" s="6" t="n">
+        <v>-0.3643</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>-5.07</v>
+        <v>-0.1101</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>14.22</v>
+        <v>-0.1051</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>-0.2066</v>
-      </c>
-      <c r="K117" s="6" t="n">
-        <v>-0.1071</v>
-      </c>
-      <c r="L117" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M117" s="4" t="inlineStr"/>
+        <v>-0.1622</v>
+      </c>
+      <c r="K117" s="4" t="n">
+        <v>-0.2542</v>
+      </c>
+      <c r="L117" s="4" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="M117" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N117" s="4" t="n"/>
+      <c r="O117" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
